--- a/event_registration_forms/012_entrepreneurial_networking_event_registration_form--event_registration_forms.xlsx
+++ b/event_registration_forms/012_entrepreneurial_networking_event_registration_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>page_1</t>
+          <t>about_yourself</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>About Your Yourself</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>page_2</t>
+          <t>are_you_a_member_of_the_entrepreneurial_network</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Are you a member of the Entrepreneurial Network?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>page_3</t>
+          <t>have_you_attended_an_entrepreneurial_network_event_before</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Have you attended an Entrepreneurial Network event before?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>page_4</t>
+          <t>what_do_you_want_to_gain_from_the_event</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What do you want to gain from the event?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>page_5</t>
+          <t>are_you_willing_to_share_your_story</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Are you willing to share your story?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>page_6</t>
+          <t>what_is_your_role</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is your role?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>page_7</t>
+          <t>how_did_you_hear_about_the_event</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>How did you hear about the event?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>page_8</t>
+          <t>what_is_your_company_name</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is your company name?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>page_9</t>
+          <t>what_is_your_title_at_your_company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is your title at your company?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>page_10</t>
+          <t>are_you_willing_to_provide_your_contact_info</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Are you willing to provide your contact information?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>page_11</t>
+          <t>consent_to_use_your_story_in_promotional_materials</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Consent to use your story in promotional materials?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>page_12</t>
+          <t>consent_to_publish_your_story_on_social_media</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Consent to publish your story on social media?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>page_13</t>
+          <t>do_you_have_a_photo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Do you have a photo?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>page_14</t>
+          <t>do_you_have_a_logo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Do you have a logo?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>page_15</t>
+          <t>do_you_have_social_media_accounts</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Do you have social media accounts?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>page_16</t>
+          <t>can_we_follow_your_account</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Can we follow your account?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>page_17</t>
+          <t>do_you_want_us_to_share_your_story_on_your_account</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Do you want us to share your story on your account?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>page_18</t>
+          <t>is_this_the_primary_contact</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Is this the primary contact?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,156 +934,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>page_19</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1098,12 +960,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,34 +988,561 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>are_you_a_member_of_the_entrepreneurial_network_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>i_am_a_member</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>I am a member</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>are_you_a_member_of_the_entrepreneurial_network_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>i_am_not_a_member</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>I am not a member</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>have_you_attended_an_entrepreneurial_network_event_before_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>have_you_attended_an_entrepreneurial_network_event_before_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>are_you_willing_to_share_your_story_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>are_you_willing_to_share_your_story_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>what_is_your_role_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ceo/founder</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CEO/Founder</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>what_is_your_role_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>investor/advisor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Investor/Advisor</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>what_is_your_role_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>how_did_you_hear_about_the_event_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>social_media</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Social Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>how_did_you_hear_about_the_event_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>friend/colleague</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Friend/Colleague</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>how_did_you_hear_about_the_event_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>online_search</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Online Search</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>are_you_willing_to_provide_your_contact_info_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>are_you_willing_to_provide_your_contact_info_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>consent_to_use_your_story_in_promotional_materials_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>i_agree</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>I agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>consent_to_use_your_story_in_promotional_materials_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>i_do_not_agree</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>I do not agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>consent_to_publish_your_story_on_social_media_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>i_agree</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>I agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>consent_to_publish_your_story_on_social_media_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>i_do_not_agree</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>I do not agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>do_you_have_a_photo_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>do_you_have_a_photo_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>do_you_have_a_logo_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>do_you_have_a_logo_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>do_you_have_social_media_accounts_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>do_you_have_social_media_accounts_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>twitter</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Twitter</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>do_you_have_social_media_accounts_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>can_we_follow_your_account_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>can_we_follow_your_account_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>twitter</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Twitter</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>can_we_follow_your_account_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>do_you_want_us_to_share_your_story_on_your_account_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>do_you_want_us_to_share_your_story_on_your_account_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>twitter</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Twitter</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>do_you_want_us_to_share_your_story_on_your_account_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>is_this_the_primary_contact_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>is_this_the_primary_contact_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
